--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134595327</v>
+        <v>134595581</v>
       </c>
       <c r="B3" t="n">
-        <v>58839</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,31 +825,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brännemossen, Brännemossen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474163</v>
+        <v>473965</v>
       </c>
       <c r="R3" t="n">
-        <v>6505842</v>
+        <v>6505790</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färsk bälgrop med fjädrar fr tjädertupp vid rotvälta.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,45 +924,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134595876</v>
+        <v>134595344</v>
       </c>
       <c r="B4" t="n">
-        <v>98060</v>
+        <v>61527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106670</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skallebolid, Skallebolid, Vg</t>
+          <t>Brännemossen, Brännemossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473910</v>
+        <v>474162</v>
       </c>
       <c r="R4" t="n">
-        <v>6505809</v>
+        <v>6505842</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -988,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,6 +1022,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,6 +1038,239 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134595327</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännemossen, Brännemossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>474163</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6505842</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134595876</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skallebolid, Skallebolid, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>473910</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505809</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,32 +924,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134595344</v>
+        <v>134595686</v>
       </c>
       <c r="B4" t="n">
-        <v>61527</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106670</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,21 +957,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännemossen, Brännemossen, Vg</t>
+          <t>Skallebolid, Skallebolid, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474162</v>
+        <v>473976</v>
       </c>
       <c r="R4" t="n">
-        <v>6505842</v>
+        <v>6505808</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1003,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1020,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med fjädrar, avbitna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1034,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,32 +1052,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134595327</v>
+        <v>134595344</v>
       </c>
       <c r="B5" t="n">
-        <v>58839</v>
+        <v>61527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>106670</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1074,28 +1085,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brännemossen, Brännemossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474163</v>
+        <v>474162</v>
       </c>
       <c r="R5" t="n">
         <v>6505842</v>
@@ -1130,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,6 +1150,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1167,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134595876</v>
+        <v>134595327</v>
       </c>
       <c r="B6" t="n">
-        <v>98060</v>
+        <v>58839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,34 +1180,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skallebolid, Skallebolid, Vg</t>
+          <t>Brännemossen, Brännemossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473910</v>
+        <v>474163</v>
       </c>
       <c r="R6" t="n">
-        <v>6505809</v>
+        <v>6505842</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1237,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1268,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,6 +1292,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134595876</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skallebolid, Skallebolid, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>473910</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6505809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134595408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134595581</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1049,6 +1064,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134595686</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134595344</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134595327</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1399,8 +1429,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134595876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,6 +1432,220 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134595876</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136042926</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98154</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bocksjö, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>474119</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6505826</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042926</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136042927</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98154</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bocksjö, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>474148</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6505854</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042927</t>
         </is>
       </c>
     </row>
@@ -1443,6 +1657,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98154</v>
+        <v>98155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98154</v>
+        <v>98155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
